--- a/光伏配储项目/电价数据/2026/元江站.xlsx
+++ b/光伏配储项目/电价数据/2026/元江站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.46052</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.6807799999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.51934</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58635</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.46682</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45668</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42397</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42522</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42227</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42548</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41338</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44475</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49777</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10851</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11903</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12727</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05502000000000001</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09734999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.07043000000000001</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.04808</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.5717100000000001</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14552</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21592</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22692</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21618</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13495</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.23274</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.0301</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.54365</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73142</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12558</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.22658</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43668</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65872</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8855700000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.49378</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.22064</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.98336</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.08227</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6942</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.30208</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.99501</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.46057</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7045399999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.74903</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.75848</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.87585</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79708</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75761</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5164299999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48014</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46743</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42571</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7099800000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.78533</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8750800000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.92118</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49592</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51636</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50381</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50402</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48625</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46825</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.91704</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.75891</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.85446</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5083799999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.49151</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.97361</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.50312</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.86191</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.82208</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.70411</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.88379</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.02259</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.9928899999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.45745</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.53654</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.48787</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.51213</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8198799999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.61413</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.73693</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.71484</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.11708</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.8895</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.1639</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.81675</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.16257</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.06471</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.2198</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.99548</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.04944</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6075</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.94213</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90461</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8676</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.58253</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.92048</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.75226</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.67624</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45031</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.77985</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80375</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44943</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42847</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33466</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50868</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48805</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48731</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44643</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44433</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.15772</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.03271</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.17074</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.04627000000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.19828</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.53118</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.78646</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.5664</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.70525</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.79553</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.51728</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.46219</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79338</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.47233</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6143099999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.5839500000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49124</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42023</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39134</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.48199</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.49929</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.56851</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.53342</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.55261</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26866</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61727</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6531</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46588</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50342</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5254</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.58288</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.53671</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6640199999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44039</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61173</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.6166900000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5622200000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7081900000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6173200000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55445</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.60788</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45707</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51918</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49581</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44259</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.41837</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.1194</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.00223</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22093</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.02428</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.21183</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.12266</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.10495</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.20876</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40657</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60915</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47559</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40091</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24328</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.26128</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.18449</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.43304</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49847</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46294</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47488</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51644</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5286000000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.47062</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50185</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31819</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.19618</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.27289</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.18003</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.2322</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.20103</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14547</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.27238</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.01934</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.20839</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.25916</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18517</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.01131</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.02668</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22137</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.19188</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.19962</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06077</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.02647</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.22235</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26228</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46464</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.49412</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34783</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.62458</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10261</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04347</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01232</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21061</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05146</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19136</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.03379</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.02539</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06475</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06297</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3336</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31554</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42792</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45594</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78528</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86981</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61779</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.54531</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20699</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41974</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41218</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43041</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.57375</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42392</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5908</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.72289</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8784999999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46767</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.56771</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.84945</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6019</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8562799999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.66574</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6557999999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59133</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.43905</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35065</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9165099999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.45559</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41439</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45295</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.48269</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.17659</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19849</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2824700000000001</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25491</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27569</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42208</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44582</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.56811</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8801100000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44889</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.15206</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69453</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7851699999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64612</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.54683</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44631</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49652</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43612</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.42835</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.48382</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43059</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43089</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.53865</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.27225</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24916</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15428</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27659</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27538</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01466</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25446</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.27253</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.55802</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.81969</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44955</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.31647</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.40761</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.26286</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27309</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16129</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.17309</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.18338</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.16337</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26647</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.17414</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25364</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.16897</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28534</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.16741</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.14424</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.13984</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.14705</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14903</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.21539</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16447</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4349</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3817</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43815</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.43015</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44114</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3423</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5172599999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.41267</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26966</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23288</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.09190000000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2098</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27392</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24055</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.26769</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.18873</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.14911</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35504</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.48462</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.49655</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37435</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.41076</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.47697</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.8655700000000001</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43568</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.54035</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.24652</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.51766</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.50035</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.24125</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.24456</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6057899999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26851</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.05949</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.80049</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.08601</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.44237</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>-0.02237</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.16401</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.79653</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.16759</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.16073</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.15254</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.16444</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.19852</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.22626</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.08187</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.11448</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.15169</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.13495</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6587999999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.65016</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.54795</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50688</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24511</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.20803</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32647</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.41477</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.16497</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.16246</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>-0.01298</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.18073</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3468</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.19617</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.04019</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.26728</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>1.3448</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>1.32463</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>1.33568</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>1.3397</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>1.35526</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>1.26881</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>1.35099</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>1.35946</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41806</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65396</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.61241</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44172</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.24225</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.43276</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.25973</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.25147</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33998</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.27002</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.16314</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.21062</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6518999999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60965</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6214700000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48209</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.81796</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.4766</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7912100000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45292</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49626</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35604</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.47421</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5558200000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.49679</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.65762</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.53559</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.48263</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4357799999999999</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.18718</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.23437</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.23362</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43149</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.26753</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.25564</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.27776</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.60641</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.21572</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.04743</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.22672</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.47692</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.4944</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.49481</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.53225</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6663300000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.78988</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.88446</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.63774</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.76413</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.61399</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.4357200000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.78755</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76788</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62087</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6695</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.41473</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46212</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45509</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5309199999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43023</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44265</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43147</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42139</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.43319</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.43702</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.41192</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.13863</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.13098</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.20324</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42927</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.43797</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40509</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.35064</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.48189</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.24015</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.25609</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.20864</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23682</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25496</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.12008</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25364</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03919</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18064</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18561</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24068</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23707</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33804</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.25858</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.27843</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.27964</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.27405</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.27633</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.28527</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19071</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23852</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01555</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>7.000000000000001e-05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14728</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02166</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01525</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04082</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04825</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.0293</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04696</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00053</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03773</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01791</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20255</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.28168</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.43701</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.34293</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7974</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6881699999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.48803</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.43223</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.44844</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.28617</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.7890199999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8825700000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85651</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12184</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.25464</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26886</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.26702</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06107</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25423</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47198</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.59853</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.82112</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.80757</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.80984</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.40426</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97873</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.80735</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.85905</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.83847</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84289</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8411000000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84536</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94245</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.8031</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.83443</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.80502</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.37132</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.48447</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.64708</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.76274</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.60685</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49694</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.49745</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.48189</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.49933</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.44465</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.4832</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1.34721</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.35032</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>1.34249</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>1.32948</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.42913</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.48004</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.80423</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41901</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.64125</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.48097</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.43264</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.50758</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34947</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.43399</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43955</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.43125</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.6065700000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.80759</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.58836</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.49646</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.59101</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.47375</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26587</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47353</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.05582</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7612100000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.48763</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>-0.02352</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.7580800000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.74439</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.59822</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.48422</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.48319</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.24341</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36138</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46737</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.13689</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.25729</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.27479</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50898</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.51666</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.09501999999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.16588</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.73492</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.41357</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.42724</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.64659</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.64251</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.72987</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.89822</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.79547</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7278600000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36571</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.12377</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.24389</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.04946</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.11287</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.24835</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.21803</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.02262</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.06823</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.24511</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.07306</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.01725</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.04351</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.26544</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.23941</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.21395</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.26465</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.36396</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.45388</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.17806</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.26794</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37346</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.93347</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56214</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.47119</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44806</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.3603</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.36194</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.15799</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.42564</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.27233</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.21675</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.3992</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38834</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.23793</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.22385</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.23566</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36405</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17586</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14553</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19832</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14175</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04508</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.11937</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22244</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.25857</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14693</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14281</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19144</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22653</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26361</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15389</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15489</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19768</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.27867</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.25017</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46467</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38862</v>
       </c>
     </row>
   </sheetData>
